--- a/notes/个人学习计划.xlsx
+++ b/notes/个人学习计划.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C569F5-77A8-44C0-ADEE-D5F2EF14A847}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856569B5-A5F2-419D-ABDC-0FD1C6E49B99}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="2055" windowWidth="22485" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2014" sheetId="4" r:id="rId1"/>
-    <sheet name="2015" sheetId="5" r:id="rId2"/>
-    <sheet name="2016" sheetId="6" r:id="rId3"/>
-    <sheet name="2017" sheetId="1" r:id="rId4"/>
-    <sheet name="2018" sheetId="2" r:id="rId5"/>
-    <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId6"/>
+    <sheet name="2017" sheetId="1" r:id="rId1"/>
+    <sheet name="2018" sheetId="2" r:id="rId2"/>
+    <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="993">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3641,101 +3638,6 @@
   </si>
   <si>
     <t>20181231</t>
-  </si>
-  <si>
-    <t>20140101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20140102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20140103</t>
-  </si>
-  <si>
-    <t>20140104</t>
-  </si>
-  <si>
-    <t>20140105</t>
-  </si>
-  <si>
-    <t>20140106</t>
-  </si>
-  <si>
-    <t>20140107</t>
-  </si>
-  <si>
-    <t>20140108</t>
-  </si>
-  <si>
-    <t>20140109</t>
-  </si>
-  <si>
-    <t>20140110</t>
-  </si>
-  <si>
-    <t>20140111</t>
-  </si>
-  <si>
-    <t>20140112</t>
-  </si>
-  <si>
-    <t>20140113</t>
-  </si>
-  <si>
-    <t>20140114</t>
-  </si>
-  <si>
-    <t>20140115</t>
-  </si>
-  <si>
-    <t>20140116</t>
-  </si>
-  <si>
-    <t>20140117</t>
-  </si>
-  <si>
-    <t>20140118</t>
-  </si>
-  <si>
-    <t>20140119</t>
-  </si>
-  <si>
-    <t>20140120</t>
-  </si>
-  <si>
-    <t>20140121</t>
-  </si>
-  <si>
-    <t>20140122</t>
-  </si>
-  <si>
-    <t>20140123</t>
-  </si>
-  <si>
-    <t>20140124</t>
-  </si>
-  <si>
-    <t>20140125</t>
-  </si>
-  <si>
-    <t>20140126</t>
-  </si>
-  <si>
-    <t>20140127</t>
-  </si>
-  <si>
-    <t>20140128</t>
-  </si>
-  <si>
-    <t>20140129</t>
-  </si>
-  <si>
-    <t>20140130</t>
-  </si>
-  <si>
-    <t>20140131</t>
   </si>
 </sst>
 </file>
@@ -4589,195 +4491,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4514419-6CED-4349-B635-0ABD8CCC504B}">
-  <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF6A1568-BDE5-48F6-AA13-ECBDD284C5A1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C7C913-161F-460E-9ACA-74EFA842A59E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G145"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -5781,7 +5494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N280"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -8281,7 +7994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/notes/个人学习计划.xlsx
+++ b/notes/个人学习计划.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\github\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856569B5-A5F2-419D-ABDC-0FD1C6E49B99}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F719FEC-84B8-40ED-95A9-7CC3315A21AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="2055" windowWidth="22485" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3168" yWindow="3168" windowWidth="17280" windowHeight="9072" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2017" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="994">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3638,6 +3638,10 @@
   </si>
   <si>
     <t>20181231</t>
+  </si>
+  <si>
+    <t>jwt 看博士的博文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4493,11 +4497,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G145"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="54.875" customWidth="1"/>
-    <col min="3" max="3" width="30.75" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4655,7 +4659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="40.5">
+    <row r="21" spans="1:4" ht="43.2">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -4674,7 +4678,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="27">
+    <row r="23" spans="1:4" ht="28.8">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -5497,14 +5501,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N280"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.25" customWidth="1"/>
+    <col min="1" max="1" width="28.21875" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="31.375" customWidth="1"/>
-    <col min="4" max="4" width="55.125" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
-    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="55.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -5624,7 +5628,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="40.5">
+    <row r="16" spans="1:14" ht="43.2">
       <c r="A16" s="1" t="s">
         <v>244</v>
       </c>
@@ -5701,7 +5705,7 @@
       </c>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="40.5">
+    <row r="22" spans="1:9" ht="43.2">
       <c r="A22" s="1" t="s">
         <v>248</v>
       </c>
@@ -5760,7 +5764,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="108">
+    <row r="28" spans="1:9" ht="115.2">
       <c r="A28" s="1" t="s">
         <v>253</v>
       </c>
@@ -5789,7 +5793,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="40.5">
+    <row r="29" spans="1:9" ht="57.6">
       <c r="A29" s="1" t="s">
         <v>254</v>
       </c>
@@ -5828,7 +5832,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27">
+    <row r="32" spans="1:9" ht="28.8">
       <c r="A32" s="1" t="s">
         <v>257</v>
       </c>
@@ -5850,7 +5854,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="27">
+    <row r="34" spans="1:6" ht="28.8">
       <c r="A34" s="1" t="s">
         <v>259</v>
       </c>
@@ -5861,7 +5865,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="27">
+    <row r="35" spans="1:6" ht="28.8">
       <c r="A35" s="1" t="s">
         <v>260</v>
       </c>
@@ -5869,7 +5873,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="54">
+    <row r="36" spans="1:6" ht="57.6">
       <c r="A36" s="1" t="s">
         <v>320</v>
       </c>
@@ -5950,7 +5954,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="40.5">
+    <row r="42" spans="1:6" ht="43.2">
       <c r="A42" s="1" t="s">
         <v>326</v>
       </c>
@@ -6023,7 +6027,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="27">
+    <row r="47" spans="1:6" ht="28.8">
       <c r="A47" s="1" t="s">
         <v>331</v>
       </c>
@@ -6050,7 +6054,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="54">
+    <row r="50" spans="1:5" ht="57.6">
       <c r="A50" s="1" t="s">
         <v>334</v>
       </c>
@@ -6075,7 +6079,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="27">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="1" t="s">
         <v>336</v>
       </c>
@@ -6149,7 +6153,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="27">
+    <row r="59" spans="1:5" ht="31.2">
       <c r="A59" s="1" t="s">
         <v>343</v>
       </c>
@@ -6166,7 +6170,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="27">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="1" t="s">
         <v>344</v>
       </c>
@@ -6180,7 +6184,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="27">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="1" t="s">
         <v>345</v>
       </c>
@@ -6202,7 +6206,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="40.5">
+    <row r="63" spans="1:5" ht="43.2">
       <c r="A63" s="1" t="s">
         <v>347</v>
       </c>
@@ -6216,7 +6220,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="27">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="1" t="s">
         <v>348</v>
       </c>
@@ -6224,7 +6228,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27">
+    <row r="65" spans="1:8" ht="43.2">
       <c r="A65" s="1" t="s">
         <v>349</v>
       </c>
@@ -6269,7 +6273,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="27">
+    <row r="71" spans="1:8" ht="28.8">
       <c r="A71" s="1" t="s">
         <v>421</v>
       </c>
@@ -6280,7 +6284,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27">
+    <row r="72" spans="1:8" ht="28.8">
       <c r="A72" s="1" t="s">
         <v>422</v>
       </c>
@@ -6296,7 +6300,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27">
+    <row r="74" spans="1:8" ht="28.8">
       <c r="A74" s="1" t="s">
         <v>424</v>
       </c>
@@ -6326,7 +6330,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27">
+    <row r="77" spans="1:8" ht="43.2">
       <c r="A77" s="1" t="s">
         <v>427</v>
       </c>
@@ -6346,7 +6350,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="94.5">
+    <row r="78" spans="1:8" ht="100.8">
       <c r="A78" s="1" t="s">
         <v>428</v>
       </c>
@@ -6372,7 +6376,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27">
+    <row r="79" spans="1:8" ht="28.8">
       <c r="A79" s="1" t="s">
         <v>429</v>
       </c>
@@ -6409,7 +6413,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="67.5">
+    <row r="84" spans="1:8" ht="72">
       <c r="A84" s="1" t="s">
         <v>434</v>
       </c>
@@ -6454,7 +6458,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27">
+    <row r="87" spans="1:8" ht="28.8">
       <c r="A87" s="1" t="s">
         <v>437</v>
       </c>
@@ -6473,7 +6477,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27">
+    <row r="89" spans="1:8" ht="28.8">
       <c r="A89" s="1" t="s">
         <v>439</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="40.5">
+    <row r="90" spans="1:8" ht="43.2">
       <c r="A90" s="1" t="s">
         <v>440</v>
       </c>
@@ -6495,7 +6499,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="27">
+    <row r="91" spans="1:8" ht="28.8">
       <c r="A91" s="1" t="s">
         <v>441</v>
       </c>
@@ -6531,7 +6535,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27">
+    <row r="94" spans="1:8" ht="28.8">
       <c r="A94" s="1" t="s">
         <v>444</v>
       </c>
@@ -6564,7 +6568,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="37.5">
+    <row r="97" spans="1:7" ht="36">
       <c r="A97" s="1" t="s">
         <v>510</v>
       </c>
@@ -6586,7 +6590,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="27">
+    <row r="99" spans="1:7" ht="28.8">
       <c r="A99" s="1" t="s">
         <v>512</v>
       </c>
@@ -6597,7 +6601,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="27">
+    <row r="100" spans="1:7" ht="28.8">
       <c r="A100" s="1" t="s">
         <v>513</v>
       </c>
@@ -6631,7 +6635,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="40.5">
+    <row r="102" spans="1:7" ht="43.2">
       <c r="A102" s="1" t="s">
         <v>515</v>
       </c>
@@ -6645,7 +6649,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="27">
+    <row r="103" spans="1:7" ht="28.8">
       <c r="A103" s="1" t="s">
         <v>516</v>
       </c>
@@ -6667,7 +6671,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="54">
+    <row r="105" spans="1:7" ht="57.6">
       <c r="A105" s="1" t="s">
         <v>518</v>
       </c>
@@ -6709,7 +6713,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="27">
+    <row r="108" spans="1:7" ht="28.8">
       <c r="A108" s="1" t="s">
         <v>521</v>
       </c>
@@ -6731,7 +6735,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="27">
+    <row r="110" spans="1:7" ht="42">
       <c r="A110" s="1" t="s">
         <v>523</v>
       </c>
@@ -6756,7 +6760,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="27">
+    <row r="112" spans="1:7" ht="28.8">
       <c r="A112" s="1" t="s">
         <v>525</v>
       </c>
@@ -6767,7 +6771,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="67.5">
+    <row r="113" spans="1:5" ht="72">
       <c r="A113" s="1" t="s">
         <v>526</v>
       </c>
@@ -6778,7 +6782,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="40.5">
+    <row r="114" spans="1:5" ht="43.2">
       <c r="A114" s="1" t="s">
         <v>527</v>
       </c>
@@ -6838,6 +6842,9 @@
       <c r="D118" t="s">
         <v>736</v>
       </c>
+      <c r="E118" t="s">
+        <v>993</v>
+      </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
@@ -6847,7 +6854,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="27">
+    <row r="120" spans="1:5" ht="28.8">
       <c r="A120" s="1" t="s">
         <v>533</v>
       </c>
@@ -6886,7 +6893,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="27">
+    <row r="123" spans="1:5" ht="28.8">
       <c r="A123" s="1" t="s">
         <v>536</v>
       </c>
@@ -6908,7 +6915,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="27">
+    <row r="125" spans="1:5" ht="28.8">
       <c r="A125" s="1" t="s">
         <v>538</v>
       </c>
@@ -6933,7 +6940,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="27">
+    <row r="127" spans="1:5" ht="28.8">
       <c r="A127" s="1" t="s">
         <v>758</v>
       </c>
@@ -6968,7 +6975,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="27">
+    <row r="131" spans="1:6" ht="28.8">
       <c r="A131" s="1" t="s">
         <v>762</v>
       </c>
@@ -7004,7 +7011,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="27">
+    <row r="134" spans="1:6" ht="28.8">
       <c r="A134" s="1" t="s">
         <v>765</v>
       </c>
@@ -7123,7 +7130,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="27">
+    <row r="144" spans="1:6" ht="28.8">
       <c r="A144" s="1" t="s">
         <v>775</v>
       </c>
@@ -7179,7 +7186,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="27">
+    <row r="151" spans="1:5" ht="28.8">
       <c r="A151" s="1" t="s">
         <v>782</v>
       </c>
@@ -7218,7 +7225,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="40.5">
+    <row r="154" spans="1:5" ht="43.2">
       <c r="A154" s="1" t="s">
         <v>785</v>
       </c>
@@ -7525,7 +7532,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="27">
+    <row r="198" spans="1:5" ht="28.8">
       <c r="A198" s="1" t="s">
         <v>884</v>
       </c>
@@ -7997,11 +8004,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="3" width="88.375" customWidth="1"/>
-    <col min="4" max="4" width="52.25" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="88.33203125" customWidth="1"/>
+    <col min="4" max="4" width="52.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8148,7 +8155,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24">
+    <row r="15" spans="1:4" ht="22.8">
       <c r="A15" s="50"/>
       <c r="B15" s="21" t="s">
         <v>620</v>
@@ -8182,7 +8189,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="24">
+    <row r="18" spans="1:4" ht="22.8">
       <c r="A18" s="39"/>
       <c r="B18" s="42"/>
       <c r="C18" s="45"/>
@@ -8210,7 +8217,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="24">
+    <row r="21" spans="1:4" ht="22.8">
       <c r="A21" s="39"/>
       <c r="B21" s="21" t="s">
         <v>636</v>
@@ -8256,7 +8263,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="24">
+    <row r="25" spans="1:4" ht="22.8">
       <c r="A25" s="39"/>
       <c r="B25" s="21" t="s">
         <v>644</v>
@@ -8290,7 +8297,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="36">
+    <row r="28" spans="1:4" ht="34.200000000000003">
       <c r="A28" s="50"/>
       <c r="B28" s="21" t="s">
         <v>650</v>
@@ -8316,7 +8323,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="24">
+    <row r="30" spans="1:4" ht="22.8">
       <c r="A30" s="39"/>
       <c r="B30" s="42"/>
       <c r="C30" s="45"/>
@@ -8474,7 +8481,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="48">
+    <row r="49" spans="1:4" ht="45.6">
       <c r="A49" s="39"/>
       <c r="B49" s="43"/>
       <c r="C49" s="20" t="s">
@@ -8504,7 +8511,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="24">
+    <row r="52" spans="1:4" ht="22.8">
       <c r="A52" s="39"/>
       <c r="B52" s="21" t="s">
         <v>648</v>
@@ -8536,7 +8543,7 @@
       </c>
       <c r="D54" s="29"/>
     </row>
-    <row r="55" spans="1:4" ht="72">
+    <row r="55" spans="1:4" ht="79.8">
       <c r="A55" s="39"/>
       <c r="B55" s="23" t="s">
         <v>686</v>
@@ -8756,7 +8763,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="36">
+    <row r="81" spans="1:4" ht="34.200000000000003">
       <c r="A81" s="39"/>
       <c r="B81" s="21" t="s">
         <v>719</v>
@@ -8790,7 +8797,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="24">
+    <row r="84" spans="1:4" ht="22.8">
       <c r="A84" s="39"/>
       <c r="B84" s="21" t="s">
         <v>725</v>
@@ -8820,7 +8827,7 @@
       </c>
       <c r="D86" s="29"/>
     </row>
-    <row r="87" spans="1:4" ht="120">
+    <row r="87" spans="1:4" ht="125.4">
       <c r="A87" s="39"/>
       <c r="B87" s="23" t="s">
         <v>729</v>
